--- a/data/trans_orig/LAWTONB_2R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>231436</t>
+          <t>232148</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>256895</t>
+          <t>257643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>258538</t>
+          <t>259994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286562</t>
+          <t>287995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>497187</t>
+          <t>500163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>536288</t>
+          <t>538779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39179</t>
+          <t>39735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>26136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46779</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>49991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80777</t>
+          <t>78768</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42490</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111916</t>
+          <t>110082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138559</t>
+          <t>138776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151550</t>
+          <t>152731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189528</t>
+          <t>188529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271318</t>
+          <t>270024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320522</t>
+          <t>317878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50256</t>
+          <t>50373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56350</t>
+          <t>56327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88144</t>
+          <t>89205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92169</t>
+          <t>93309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130198</t>
+          <t>130672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35001</t>
+          <t>33126</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62562</t>
+          <t>60441</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47171</t>
+          <t>47458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77922</t>
+          <t>78870</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>29416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>24706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46903</t>
+          <t>46872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>43419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56142</t>
+          <t>58215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>349048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>784663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>846564</t>
+          <t>844615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84918</t>
+          <t>83890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89243</t>
+          <t>87911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127226</t>
+          <t>126236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149667</t>
+          <t>151409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198546</t>
+          <t>199983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>39285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>81615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>73074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>110932</t>
+          <t>110447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29573</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39582</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>50238</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69230</t>
+          <t>68586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>249569</t>
+          <t>247064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274711</t>
+          <t>274316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>261478</t>
+          <t>261901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>292940</t>
+          <t>294317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>522225</t>
+          <t>518053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>562186</t>
+          <t>561685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24675</t>
+          <t>24885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48440</t>
+          <t>47496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38356</t>
+          <t>39536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65873</t>
+          <t>67327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25759</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>36349</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>40024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28655</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128445</t>
+          <t>129595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163235</t>
+          <t>162988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156267</t>
+          <t>156486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197778</t>
+          <t>197884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296135</t>
+          <t>295382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349221</t>
+          <t>348570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43769</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73723</t>
+          <t>72639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59191</t>
+          <t>58012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92015</t>
+          <t>91481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>47358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55412</t>
+          <t>56430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58708</t>
+          <t>57778</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93138</t>
+          <t>92959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37238</t>
+          <t>37419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42297</t>
+          <t>41840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>70331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63474</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99887</t>
+          <t>100016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44919</t>
+          <t>44212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74756</t>
+          <t>73732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67684</t>
+          <t>67355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103814</t>
+          <t>106856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>426598</t>
+          <t>429223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>482258</t>
+          <t>484289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>831877</t>
+          <t>832845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>901880</t>
+          <t>901708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>45741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75582</t>
+          <t>73932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112641</t>
+          <t>111442</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104504</t>
+          <t>102540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148635</t>
+          <t>146729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31323</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56317</t>
+          <t>57445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43496</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82799</t>
+          <t>81371</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121688</t>
+          <t>122123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52979</t>
+          <t>52718</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>86074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87491</t>
+          <t>86851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129725</t>
+          <t>129034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>48620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54544</t>
+          <t>52794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87232</t>
+          <t>86327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84516</t>
+          <t>84710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128250</t>
+          <t>125360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>289138</t>
+          <t>288609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310882</t>
+          <t>310626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>272378</t>
+          <t>277983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>307638</t>
+          <t>309335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>575838</t>
+          <t>573485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>613317</t>
+          <t>614153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36005</t>
+          <t>35820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64852</t>
+          <t>63206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>46945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76800</t>
+          <t>77048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>32895</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43528</t>
+          <t>43895</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29718</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152609</t>
+          <t>151419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179106</t>
+          <t>180272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182763</t>
+          <t>185816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229043</t>
+          <t>229858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344363</t>
+          <t>346862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>398991</t>
+          <t>398986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>32984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62444</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53971</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87314</t>
+          <t>87001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43464</t>
+          <t>42386</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>41811</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71217</t>
+          <t>73238</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71726</t>
+          <t>69952</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108337</t>
+          <t>108860</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32357</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39932</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70847</t>
+          <t>69178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>60927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96930</t>
+          <t>95037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>26563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>54438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36998</t>
+          <t>36992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67471</t>
+          <t>66749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>447386</t>
+          <t>448311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>485687</t>
+          <t>485461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>471482</t>
+          <t>472476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>526834</t>
+          <t>529819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>930435</t>
+          <t>936095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1001458</t>
+          <t>1004925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46963</t>
+          <t>46607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75655</t>
+          <t>78382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117029</t>
+          <t>116495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108426</t>
+          <t>106710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152714</t>
+          <t>151667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62970</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>97479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>97756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142731</t>
+          <t>139897</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>42873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49893</t>
+          <t>47955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83183</t>
+          <t>82491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77475</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117537</t>
+          <t>117185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58050</t>
+          <t>57102</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>75338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -7556,32 +7556,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>312973</t>
+          <t>347050</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>302461</t>
+          <t>334525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>322462</t>
+          <t>358314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7591,32 +7591,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>525499</t>
+          <t>347823</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>478517</t>
+          <t>335108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>571655</t>
+          <t>360124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7626,32 +7626,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>838473</t>
+          <t>694873</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>796054</t>
+          <t>678743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>899999</t>
+          <t>711629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -7669,32 +7669,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>20184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>38412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7704,32 +7704,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42016</t>
+          <t>45567</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>37026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67799</t>
+          <t>56106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7739,32 +7739,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>73535</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34596</t>
+          <t>60219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89256</t>
+          <t>86591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -7782,32 +7782,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7852,32 +7852,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30887</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44192</t>
+          <t>42347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -7895,32 +7895,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23240</t>
+          <t>23880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7965,32 +7965,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>35542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -8008,32 +8008,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8078,32 +8078,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8121,17 +8121,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8156,17 +8156,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>168426</t>
+          <t>187700</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154270</t>
+          <t>173473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180424</t>
+          <t>201211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>162837</t>
+          <t>179633</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150235</t>
+          <t>165454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176529</t>
+          <t>195779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8308,32 +8308,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>331263</t>
+          <t>367333</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312143</t>
+          <t>346389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>351092</t>
+          <t>388933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8351,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31346</t>
+          <t>33950</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8386,32 +8386,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64795</t>
+          <t>69813</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54844</t>
+          <t>58935</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75499</t>
+          <t>80995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8421,32 +8421,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>96141</t>
+          <t>103763</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>89804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109445</t>
+          <t>119995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -8464,32 +8464,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28144</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61334</t>
+          <t>66586</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51683</t>
+          <t>56211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71679</t>
+          <t>78279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8534,32 +8534,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>81949</t>
+          <t>88509</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>102340</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -8577,32 +8577,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39225</t>
+          <t>42280</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71639</t>
+          <t>78700</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>67253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82887</t>
+          <t>93310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8647,32 +8647,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>110865</t>
+          <t>120980</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96129</t>
+          <t>106304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126115</t>
+          <t>139260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -8690,32 +8690,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28213</t>
+          <t>29613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62030</t>
+          <t>66166</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53319</t>
+          <t>55146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>77933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8760,32 +8760,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>82366</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>74348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96553</t>
+          <t>100946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -8803,17 +8803,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8873,17 +8873,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8920,32 +8920,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>481399</t>
+          <t>534750</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>463502</t>
+          <t>513174</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>498815</t>
+          <t>551253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8955,32 +8955,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>688337</t>
+          <t>527456</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>595479</t>
+          <t>507958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>849988</t>
+          <t>549256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8990,32 +8990,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1169736</t>
+          <t>1062206</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1086845</t>
+          <t>1031392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1328904</t>
+          <t>1090849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -9033,32 +9033,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>61919</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68802</t>
+          <t>76329</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9068,32 +9068,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>106811</t>
+          <t>115380</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53081</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139099</t>
+          <t>131004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9103,32 +9103,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>163185</t>
+          <t>177298</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>158457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194789</t>
+          <t>197699</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -9146,32 +9146,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>35789</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>46772</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>72996</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104551</t>
+          <t>99816</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9216,32 +9216,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>112836</t>
+          <t>121676</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75234</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135914</t>
+          <t>139371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -9259,32 +9259,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48668</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>65052</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>85257</t>
+          <t>95315</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113117</t>
+          <t>108723</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9329,32 +9329,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>133925</t>
+          <t>147500</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88758</t>
+          <t>130300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>159873</t>
+          <t>164443</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -9372,32 +9372,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>69419</t>
+          <t>74181</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36036</t>
+          <t>63349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>86937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>93947</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>86104</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114281</t>
+          <t>115164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -9485,17 +9485,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9520,17 +9520,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9555,17 +9555,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
